--- a/blsz_stat.xlsx
+++ b/blsz_stat.xlsx
@@ -8275,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA73" t="n">
         <v>5</v>
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA74" t="n">
         <v>5</v>
@@ -18129,10 +18129,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z166" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA166" t="n">
         <v>2</v>
@@ -19021,7 +19021,7 @@
         <v>11</v>
       </c>
       <c r="O174" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P174" t="n">
         <v>70</v>
@@ -19053,10 +19053,10 @@
         <v>36</v>
       </c>
       <c r="Y174" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA174" t="n">
         <v>6</v>
@@ -19132,7 +19132,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O175" t="n">
         <v>29</v>
@@ -19161,10 +19161,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z175" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA175" t="n">
         <v>2</v>
@@ -19179,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF175" t="n">
         <v>1</v>
@@ -19281,13 +19281,13 @@
         <v>18</v>
       </c>
       <c r="Y176" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z176" t="n">
         <v>11</v>
       </c>
       <c r="AA176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB176" t="n">
         <v>0</v>
@@ -20384,10 +20384,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O186" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P186" t="n">
         <v>50</v>
@@ -20413,13 +20413,13 @@
         <v>90</v>
       </c>
       <c r="Y186" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z186" t="n">
         <v>20</v>
       </c>
       <c r="AA186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB186" t="n">
         <v>0</v>
@@ -20608,7 +20608,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O188" t="n">
         <v>63</v>
@@ -20643,11 +20643,11 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z188" t="n">
         <v>27</v>
       </c>
-      <c r="Z188" t="n">
-        <v>26</v>
-      </c>
       <c r="AA188" t="n">
         <v>1</v>
       </c>
@@ -20661,7 +20661,7 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF188" t="n">
         <v>0</v>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O189" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P189" t="n">
         <v>50</v>
@@ -20757,10 +20757,10 @@
         <v>18</v>
       </c>
       <c r="Y189" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z189" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA189" t="n">
         <v>3</v>
@@ -21427,10 +21427,10 @@
         <v>54</v>
       </c>
       <c r="Y195" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z195" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA195" t="n">
         <v>9</v>
@@ -21515,7 +21515,7 @@
         <v>4</v>
       </c>
       <c r="O196" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P196" t="n">
         <v>80</v>
@@ -21547,10 +21547,10 @@
         <v>54</v>
       </c>
       <c r="Y196" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z196" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -21661,10 +21661,10 @@
         <v>18</v>
       </c>
       <c r="Y197" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z197" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA197" t="n">
         <v>8</v>
@@ -32121,10 +32121,10 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z292" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA292" t="n">
         <v>10</v>
@@ -32905,10 +32905,10 @@
         <v>36</v>
       </c>
       <c r="Y299" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z299" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA299" t="n">
         <v>1</v>
@@ -34229,10 +34229,10 @@
         <v>18</v>
       </c>
       <c r="Y311" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z311" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA311" t="n">
         <v>3</v>
@@ -34618,7 +34618,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O315" t="n">
         <v>24</v>
@@ -34653,13 +34653,13 @@
         <v>0</v>
       </c>
       <c r="Y315" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z315" t="n">
         <v>13</v>
       </c>
       <c r="AA315" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB315" t="n">
         <v>2</v>
@@ -34732,10 +34732,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O316" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P316" t="n">
         <v>60</v>
@@ -34767,10 +34767,10 @@
         <v>18</v>
       </c>
       <c r="Y316" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z316" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA316" t="n">
         <v>4</v>
@@ -34985,10 +34985,10 @@
         <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z318" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA318" t="n">
         <v>6</v>
@@ -35209,10 +35209,10 @@
         <v>27</v>
       </c>
       <c r="Y320" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z320" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA320" t="n">
         <v>20</v>
@@ -35406,7 +35406,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O322" t="n">
         <v>37</v>
@@ -35441,13 +35441,13 @@
         <v>26</v>
       </c>
       <c r="Y322" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z322" t="n">
         <v>15</v>
       </c>
       <c r="AA322" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB322" t="n">
         <v>1</v>
@@ -36644,7 +36644,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O333" t="n">
         <v>43</v>
@@ -36679,10 +36679,10 @@
         <v>0</v>
       </c>
       <c r="Y333" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z333" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA333" t="n">
         <v>0</v>
@@ -37009,10 +37009,10 @@
         <v>5</v>
       </c>
       <c r="Y336" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z336" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA336" t="n">
         <v>7</v>
@@ -37021,7 +37021,7 @@
         <v>1</v>
       </c>
       <c r="AC336" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD336" t="n">
         <v>0</v>
@@ -37241,10 +37241,10 @@
         <v>0</v>
       </c>
       <c r="Y338" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z338" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA338" t="n">
         <v>8</v>
@@ -48742,7 +48742,7 @@
         </is>
       </c>
       <c r="U9" s="8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="V9" s="8" t="n">
         <v>57.9</v>
@@ -50154,7 +50154,7 @@
         </is>
       </c>
       <c r="U22" s="8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>57.9</v>
@@ -52510,7 +52510,7 @@
         </is>
       </c>
       <c r="U43" s="8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="V43" s="8" t="n">
         <v>57.9</v>
@@ -54174,7 +54174,7 @@
         <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" t="n">
         <v>0.21</v>
@@ -54924,10 +54924,10 @@
         <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
@@ -56124,10 +56124,10 @@
         <v>3</v>
       </c>
       <c r="M64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N64" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="65">
@@ -56515,19 +56515,19 @@
         <v>0.5</v>
       </c>
       <c r="J72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N72" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="73">
@@ -56724,7 +56724,7 @@
         <v>8</v>
       </c>
       <c r="M76" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N76" t="n">
         <v>0.14</v>
@@ -56774,7 +56774,7 @@
         <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N77" t="n">
         <v>0.05</v>
@@ -56924,7 +56924,7 @@
         <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N80" t="n">
         <v>0.07000000000000001</v>
@@ -57174,7 +57174,7 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N85" t="n">
         <v>0.03</v>
@@ -57274,10 +57274,10 @@
         <v>6</v>
       </c>
       <c r="M87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N87" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="88">
@@ -58074,7 +58074,7 @@
         <v>3</v>
       </c>
       <c r="M103" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N103" t="n">
         <v>0.07000000000000001</v>
@@ -59074,10 +59074,10 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N123" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="124">
@@ -61424,7 +61424,7 @@
         <v>8</v>
       </c>
       <c r="M170" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N170" t="n">
         <v>0.12</v>
@@ -61524,10 +61524,10 @@
         <v>7</v>
       </c>
       <c r="M172" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N172" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="173">
@@ -61691,12 +61691,12 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER FERENC JAKAB</t>
+          <t>LACZKOVICS MARTIN ZOLTÁN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://adatbank.mlsz.hu/player/475873.html</t>
+          <t>https://adatbank.mlsz.hu/player/194088.html</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -61709,25 +61709,25 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M176" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N176" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="177">
@@ -61736,17 +61736,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RÁKOSSZENTMIHÁLYI SC</t>
+          <t>INTER 04 II.</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>KASINSZKY ISTVÁN</t>
+          <t>HOCHSCHORNER FERENC JAKAB</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://adatbank.mlsz.hu/player/16770.html</t>
+          <t>https://adatbank.mlsz.hu/player/475873.html</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -61774,10 +61774,10 @@
         <v>4</v>
       </c>
       <c r="M177" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="N177" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="178">
@@ -61786,17 +61786,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>INTER 04 II.</t>
+          <t>RÁKOSSZENTMIHÁLYI SC</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>LACZKOVICS MARTIN ZOLTÁN</t>
+          <t>KASINSZKY ISTVÁN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://adatbank.mlsz.hu/player/194088.html</t>
+          <t>https://adatbank.mlsz.hu/player/16770.html</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -61809,7 +61809,7 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
@@ -61824,10 +61824,10 @@
         <v>4</v>
       </c>
       <c r="M178" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N178" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="179">
@@ -62024,10 +62024,10 @@
         <v>4</v>
       </c>
       <c r="M182" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N182" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="183">
@@ -62274,10 +62274,10 @@
         <v>3</v>
       </c>
       <c r="M187" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N187" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="188">
@@ -62524,7 +62524,7 @@
         <v>3</v>
       </c>
       <c r="M192" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N192" t="n">
         <v>0.11</v>
@@ -63924,10 +63924,10 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N220" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="221">
@@ -64424,7 +64424,7 @@
         <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N230" t="n">
         <v>0.03</v>
@@ -64624,7 +64624,7 @@
         <v>1</v>
       </c>
       <c r="M234" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N234" t="n">
         <v>0.08</v>
@@ -66528,10 +66528,10 @@
         <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="17">
@@ -66946,10 +66946,10 @@
         <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="28">
@@ -67554,10 +67554,10 @@
         <v>26</v>
       </c>
       <c r="I43" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="44">
@@ -67972,10 +67972,10 @@
         <v>5</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="55">
@@ -68314,7 +68314,7 @@
         <v>13</v>
       </c>
       <c r="I63" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J63" t="n">
         <v>0.3</v>
@@ -69036,10 +69036,10 @@
         <v>4</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="83">
@@ -69188,7 +69188,7 @@
         <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
         <v>0.1</v>
@@ -69568,7 +69568,7 @@
         <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J96" t="n">
         <v>0.11</v>
@@ -69682,10 +69682,10 @@
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J99" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100">
@@ -70442,10 +70442,10 @@
         <v>12</v>
       </c>
       <c r="I119" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J119" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="120">
@@ -70480,7 +70480,7 @@
         <v>5</v>
       </c>
       <c r="I120" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J120" t="n">
         <v>0.14</v>
@@ -70746,7 +70746,7 @@
         <v>17</v>
       </c>
       <c r="I127" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J127" t="n">
         <v>0.29</v>
@@ -70758,17 +70758,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1908 SZAC BUDAPEST II.</t>
+          <t>NIMRÓD SE II.</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>TOMPOS TAMÁS FUMIAKI</t>
+          <t>VARGA ZOLTÁN ISTVÁN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://adatbank.mlsz.hu/player/471177.html</t>
+          <t>https://adatbank.mlsz.hu/player/1228427.html</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -70781,13 +70781,13 @@
         <v>0.25</v>
       </c>
       <c r="H128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I128" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J128" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="129">
@@ -70796,17 +70796,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NIMRÓD SE II.</t>
+          <t>1908 SZAC BUDAPEST II.</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>VARGA ZOLTÁN ISTVÁN</t>
+          <t>TOMPOS TAMÁS FUMIAKI</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://adatbank.mlsz.hu/player/1228427.html</t>
+          <t>https://adatbank.mlsz.hu/player/471177.html</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -70822,10 +70822,10 @@
         <v>9</v>
       </c>
       <c r="I129" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J129" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="130">
@@ -70936,10 +70936,10 @@
         <v>5</v>
       </c>
       <c r="I132" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J132" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="133">
@@ -73786,10 +73786,10 @@
         <v>3</v>
       </c>
       <c r="I207" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J207" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="208">
@@ -74014,10 +74014,10 @@
         <v>3</v>
       </c>
       <c r="I213" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J213" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -74888,7 +74888,7 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J236" t="n">
         <v>0.04</v>
@@ -75496,7 +75496,7 @@
         <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J252" t="n">
         <v>0.08</v>
